--- a/outputs/marine_equipment/План_2_контейнера.xlsx
+++ b/outputs/marine_equipment/План_2_контейнера.xlsx
@@ -11290,7 +11290,7 @@
       </c>
       <c r="B188" s="23" t="inlineStr">
         <is>
-          <t>Сплошной настил доской 40 мм под первый ярус</t>
+          <t>Сплошной настил необрезной доской 25 мм под первый ярус</t>
         </is>
       </c>
       <c r="C188" s="23" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="C189" s="15" t="inlineStr">
         <is>
-          <t>Доска 40 мм поперек, на всю ширину</t>
+          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
         </is>
       </c>
       <c r="D189" s="16" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C190" s="15" t="inlineStr">
         <is>
-          <t>Доска 25-40 мм поперек</t>
+          <t>Необрезная доска 25 мм поперек</t>
         </is>
       </c>
       <c r="D190" s="16" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B100" s="23" t="inlineStr">
         <is>
-          <t>Сплошной настил доской 40 мм под первый ярус</t>
+          <t>Сплошной настил необрезной доской 25 мм под первый ярус</t>
         </is>
       </c>
       <c r="C100" s="23" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Доска 40 мм поперек, на всю ширину</t>
+          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
         </is>
       </c>
       <c r="D101" s="16" t="n">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Доска 25-40 мм поперек</t>
+          <t>Необрезная доска 25 мм поперек</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Между рядами кладем доску 25-40 мм на всю ширину. Штабель без прокладок за дорогу садится, и нижний ряд принимает вес всего штабеля точечно.</t>
+          <t>Между рядами кладем необрезную доску 25 мм на всю ширину. Под тяжелыми задвижками доски кладем чаще, с шагом 300-400 мм: двадцатипятка держит, если опереть ее почаще. Штабель без прокладок за дорогу садится, и нижний ряд принимает вес всего штабеля точечно.</t>
         </is>
       </c>
     </row>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Сначала настил доской 40 мм на пол контейнера. На него задвижки Ду350, Ду300, Ду250 и Ду200, ближе к середине длины. Сверху доска, на нее остальная арматура Ду100-150, снова доска, на нее ящики с мелкими клапанами, и только сверху фильтры. Доска обязательна и под нижним ярусом, и между каждыми двумя ярусами: без нее фланец верхнего ряда стоит на маховике нижнего.</t>
+          <t>Сначала настил необрезной доской 25 мм на пол контейнера. На него задвижки Ду350, Ду300, Ду250 и Ду200, ближе к середине длины. Сверху доска, на нее остальная арматура Ду100-150, снова доска, на нее ящики с мелкими клапанами, и только сверху фильтры. Доска обязательна и под нижним ярусом, и между каждыми двумя ярусами: без нее фланец верхнего ряда стоит на маховике нижнего.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/План_2_контейнера.xlsx
+++ b/outputs/marine_equipment/План_2_контейнера.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D161" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E161" s="14" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="D169" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="D171" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr"/>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан паровой</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr"/>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="D65" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr"/>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>колонка указательная</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">

--- a/outputs/marine_equipment/План_2_контейнера.xlsx
+++ b/outputs/marine_equipment/План_2_контейнера.xlsx
@@ -1243,22 +1243,22 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду150</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду65</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -1267,23 +1267,23 @@
         </is>
       </c>
       <c r="H10" s="14" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>288</v>
+        <v>75</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>432000</v>
+        <v>80000</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1500</v>
+        <v>1067</v>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">
@@ -1304,22 +1304,22 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду150</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -1328,23 +1328,23 @@
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>189000</v>
+        <v>80000</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1227</v>
+        <v>1067</v>
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -1360,57 +1360,53 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3. Остальная бронза и латунь</t>
+          <t>4. Прочее, по цене за килограмм</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+          <t>Клапан проходной ДУ 125 корпус</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr"/>
       <c r="H12" s="14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>504</v>
+        <v>5</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>0.54</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>576000</v>
+        <v>37000</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>1143</v>
+        <v>7400</v>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N12" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr"/>
@@ -1421,48 +1417,44 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3. Остальная бронза и латунь</t>
+          <t>4. Прочее, по цене за килограмм</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Ду60</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>18000</v>
+        <v>480000</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>1125</v>
+        <v>1778</v>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
@@ -1474,7 +1466,11 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O13" s="14" t="inlineStr"/>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
@@ -1487,7 +1483,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -1497,12 +1493,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Ду150</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -1511,23 +1507,23 @@
         </is>
       </c>
       <c r="H14" s="14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I14" s="16" t="n">
         <v>75</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>0.1</v>
+        <v>0.045</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>80000</v>
+        <v>144000</v>
       </c>
       <c r="L14" s="16" t="n">
-        <v>1067</v>
+        <v>1920</v>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -1558,12 +1554,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Ду150</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -1575,20 +1571,20 @@
         <v>1</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.1</v>
+        <v>0.008</v>
       </c>
       <c r="K15" s="16" t="n">
-        <v>80000</v>
+        <v>18000</v>
       </c>
       <c r="L15" s="16" t="n">
-        <v>1067</v>
+        <v>1800</v>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -1609,22 +1605,22 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
+          <t>Клапан фланцевый угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
@@ -1633,19 +1629,19 @@
         </is>
       </c>
       <c r="H16" s="14" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>1232</v>
+        <v>98</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>1.32</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K16" s="16" t="n">
-        <v>1056000</v>
+        <v>157500</v>
       </c>
       <c r="L16" s="16" t="n">
-        <v>857</v>
+        <v>1607</v>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="N16" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr"/>
@@ -1670,22 +1666,22 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100</t>
+          <t>Клапан фланцевый угловой Ду40 Ру10</t>
         </is>
       </c>
       <c r="G17" s="18" t="inlineStr">
@@ -1694,23 +1690,23 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>0.27</v>
+        <v>0.008</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>228000</v>
+        <v>16000</v>
       </c>
       <c r="L17" s="16" t="n">
-        <v>844</v>
+        <v>1600</v>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
@@ -1731,7 +1727,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -1741,12 +1737,12 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100</t>
+          <t>Задвижка клинкетная Ду65</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
@@ -1755,23 +1751,23 @@
         </is>
       </c>
       <c r="H18" s="14" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>1935</v>
+        <v>288</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>1.935</v>
+        <v>0.32</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>1634000</v>
+        <v>432000</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>844</v>
+        <v>1500</v>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
@@ -1792,22 +1788,22 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="G19" s="18" t="inlineStr">
@@ -1816,28 +1812,28 @@
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>70000</v>
+        <v>162000</v>
       </c>
       <c r="L19" s="16" t="n">
-        <v>778</v>
+        <v>1350</v>
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr"/>
@@ -1848,53 +1844,57 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4. Прочее, по цене за килограмм</t>
+          <t>3. Остальная бронза и латунь</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>клапан без описания — уточнить</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr"/>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="H20" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="J20" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="K20" s="16" t="n">
-        <v>37000</v>
+        <v>81000</v>
       </c>
       <c r="L20" s="16" t="n">
-        <v>7400</v>
+        <v>1350</v>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr"/>
@@ -1905,44 +1905,48 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4. Прочее, по цене за килограмм</t>
+          <t>3. Остальная бронза и латунь</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr"/>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="H21" s="14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>0.012</v>
+        <v>0.24</v>
       </c>
       <c r="K21" s="16" t="n">
-        <v>25000</v>
+        <v>324000</v>
       </c>
       <c r="L21" s="16" t="n">
-        <v>2083</v>
+        <v>1350</v>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
@@ -1951,7 +1955,7 @@
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr"/>
@@ -1967,22 +1971,22 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">
@@ -1991,23 +1995,23 @@
         </is>
       </c>
       <c r="H22" s="14" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>0.045</v>
+        <v>0.154</v>
       </c>
       <c r="K22" s="16" t="n">
-        <v>144000</v>
+        <v>189000</v>
       </c>
       <c r="L22" s="16" t="n">
-        <v>1920</v>
+        <v>1227</v>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -2028,7 +2032,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -2038,12 +2042,12 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25</t>
+          <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr">
@@ -2052,23 +2056,23 @@
         </is>
       </c>
       <c r="H23" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.008</v>
+        <v>0.21</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>18000</v>
+        <v>238000</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>1800</v>
+        <v>1214</v>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
@@ -2089,22 +2093,22 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50 Ру25</t>
+          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -2113,19 +2117,19 @@
         </is>
       </c>
       <c r="H24" s="14" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>98</v>
+        <v>504</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>157500</v>
+        <v>576000</v>
       </c>
       <c r="L24" s="16" t="n">
-        <v>1607</v>
+        <v>1143</v>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
@@ -2150,22 +2154,22 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду60</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру10</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
@@ -2177,20 +2181,20 @@
         <v>1</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="K25" s="16" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="L25" s="16" t="n">
-        <v>1600</v>
+        <v>1125</v>
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
@@ -2211,22 +2215,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -2235,19 +2239,19 @@
         </is>
       </c>
       <c r="H26" s="14" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>120</v>
+        <v>1232</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>0.12</v>
+        <v>1.32</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>162000</v>
+        <v>1056000</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>1350</v>
+        <v>857</v>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
@@ -2256,7 +2260,7 @@
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr"/>
@@ -2272,22 +2276,22 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Задвижка клинкетная Ду100</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
@@ -2296,23 +2300,23 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="K27" s="16" t="n">
-        <v>81000</v>
+        <v>228000</v>
       </c>
       <c r="L27" s="16" t="n">
-        <v>1350</v>
+        <v>844</v>
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N27" s="14" t="inlineStr">
@@ -2333,22 +2337,22 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Задвижка клинкетная Ду100</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -2357,23 +2361,23 @@
         </is>
       </c>
       <c r="H28" s="14" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>240</v>
+        <v>1935</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>0.24</v>
+        <v>1.935</v>
       </c>
       <c r="K28" s="16" t="n">
-        <v>324000</v>
+        <v>1634000</v>
       </c>
       <c r="L28" s="16" t="n">
-        <v>1350</v>
+        <v>844</v>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
@@ -2394,22 +2398,22 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
@@ -2418,28 +2422,28 @@
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="K29" s="16" t="n">
-        <v>238000</v>
+        <v>70000</v>
       </c>
       <c r="L29" s="16" t="n">
-        <v>1214</v>
+        <v>778</v>
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr"/>
@@ -2455,12 +2459,12 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -2470,7 +2474,7 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr"/>
@@ -2496,7 +2500,7 @@
       </c>
       <c r="N30" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O30" s="14" t="inlineStr"/>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -2527,7 +2531,7 @@
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr"/>
@@ -2569,44 +2573,48 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>клапан без описания — уточнить</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr"/>
+          <t>захлопка</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr"/>
       <c r="H32" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="K32" s="16" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="L32" s="16" t="n">
-        <v>2000</v>
+        <v>2083</v>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N32" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="O32" s="14" t="inlineStr"/>
@@ -2622,48 +2630,44 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+          <t>Судовая запорная арматура</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr"/>
       <c r="H33" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K33" s="16" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="L33" s="16" t="n">
-        <v>1786</v>
+        <v>2000</v>
       </c>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="O33" s="14" t="inlineStr"/>
@@ -2679,12 +2683,12 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
@@ -2694,21 +2698,21 @@
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr"/>
       <c r="H34" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>75000</v>
+        <v>25000</v>
       </c>
       <c r="L34" s="16" t="n">
         <v>1786</v>
@@ -2720,7 +2724,7 @@
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O34" s="14" t="inlineStr"/>
@@ -2736,7 +2740,7 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -2756,16 +2760,16 @@
       </c>
       <c r="G35" s="14" t="inlineStr"/>
       <c r="H35" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="K35" s="16" t="n">
-        <v>25000</v>
+        <v>75000</v>
       </c>
       <c r="L35" s="16" t="n">
         <v>1786</v>
@@ -2793,7 +2797,7 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -2813,16 +2817,16 @@
       </c>
       <c r="G36" s="14" t="inlineStr"/>
       <c r="H36" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>0.024</v>
+        <v>0.012</v>
       </c>
       <c r="K36" s="16" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="L36" s="16" t="n">
         <v>1786</v>
@@ -2850,39 +2854,39 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr"/>
       <c r="H37" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>0.18</v>
+        <v>0.024</v>
       </c>
       <c r="K37" s="16" t="n">
-        <v>480000</v>
+        <v>50000</v>
       </c>
       <c r="L37" s="16" t="n">
-        <v>1778</v>
+        <v>1786</v>
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
@@ -2891,14 +2895,10 @@
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O37" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="O37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D155" s="14" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="C157" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D157" s="14" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D158" s="14" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="C159" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D159" s="14" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="C160" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D160" s="14" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="C161" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D161" s="14" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="C162" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D162" s="14" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="C163" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D163" s="14" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="C164" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D164" s="14" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="C165" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D165" s="14" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="C166" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D166" s="14" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="C167" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D167" s="14" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="C168" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D168" s="14" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="C169" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D169" s="14" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="C170" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D170" s="14" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C171" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D171" s="14" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="C172" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D172" s="14" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="C173" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D173" s="14" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="C174" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D174" s="14" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C175" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D175" s="14" t="inlineStr">
@@ -11312,12 +11312,12 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Задвижки и клинкеты Ду200, 250, 300, 350</t>
+          <t>Клинкеты Ду200, 250, 300, 350 — один слой</t>
         </is>
       </c>
       <c r="C189" s="15" t="inlineStr">
         <is>
-          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
+          <t>Необрезная доска 25 мм сплошным настилом поверх слоя</t>
         </is>
       </c>
       <c r="D189" s="16" t="n">
@@ -11327,12 +11327,12 @@
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
+          <t>Клапанные коробки и тяжелая арматура от Ду100</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr">
@@ -11341,27 +11341,27 @@
         </is>
       </c>
       <c r="D190" s="16" t="n">
-        <v>4656</v>
+        <v>425</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Ящики с мелкой арматурой до Ду80</t>
+          <t>Ящики с мелкой арматурой, включая клинкеты до Ду150</t>
         </is>
       </c>
       <c r="C191" s="15" t="inlineStr">
         <is>
-          <t>Сплошной настил доской по верху ящиков, под верхний ярус</t>
+          <t>Два яруса ящиков высотой не больше 0,91 м каждый</t>
         </is>
       </c>
       <c r="D191" s="16" t="n">
-        <v>3902</v>
+        <v>8134</v>
       </c>
     </row>
     <row r="192">
@@ -11640,47 +11640,55 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr"/>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr"/>
       <c r="H7" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>0.01</v>
+        <v>0.048</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>50000</v>
+        <v>140000</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
-        </is>
-      </c>
-      <c r="O7" s="14" t="inlineStr"/>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
@@ -11693,51 +11701,55 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr"/>
       <c r="H8" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>0.48</v>
+        <v>0.06</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>450000</v>
+        <v>120000</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>1154</v>
+        <v>1333</v>
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O8" s="14" t="inlineStr"/>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -11750,48 +11762,48 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr"/>
       <c r="H9" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>35</v>
+        <v>390</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.045</v>
+        <v>0.48</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>40000</v>
+        <v>450000</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>1143</v>
+        <v>1154</v>
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Поддон с обрешеткой, крепление к полу</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr"/>
@@ -11807,7 +11819,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -11822,21 +11834,21 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr"/>
       <c r="H10" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.135</v>
+        <v>0.045</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="L10" s="16" t="n">
         <v>1143</v>
@@ -11864,7 +11876,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -11879,21 +11891,21 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr"/>
       <c r="H11" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>0.045</v>
+        <v>0.135</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="L11" s="16" t="n">
         <v>1143</v>
@@ -11921,7 +11933,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -11936,7 +11948,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру10</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr"/>
@@ -11978,22 +11990,22 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Ду60</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
+          <t>Захлопка фланцевая угловая Ду100Ру10</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr"/>
@@ -12001,25 +12013,25 @@
         <v>1</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>1125</v>
+        <v>1143</v>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr"/>
@@ -12035,7 +12047,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -12092,7 +12104,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -12149,43 +12161,43 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200 Ру6</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr"/>
       <c r="H16" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="K16" s="16" t="n">
-        <v>120000</v>
+        <v>88000</v>
       </c>
       <c r="L16" s="16" t="n">
-        <v>923</v>
+        <v>978</v>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -12193,7 +12205,11 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O16" s="14" t="inlineStr"/>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
@@ -12206,12 +12222,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -12221,24 +12237,24 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>56</v>
+        <v>675</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>48000</v>
+        <v>660000</v>
       </c>
       <c r="L17" s="16" t="n">
-        <v>857</v>
+        <v>978</v>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
@@ -12247,10 +12263,14 @@
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr"/>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O17" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n">
@@ -12263,7 +12283,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -12273,38 +12293,38 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
+          <t>Клапан фланцевый проходной Ду200 Ру6</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr"/>
       <c r="H18" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>0.225</v>
+        <v>0.16</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>170000</v>
+        <v>120000</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>850</v>
+        <v>923</v>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Поддон с обрешеткой, крепление к полу</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr"/>
@@ -12320,7 +12340,7 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -12330,29 +12350,29 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr"/>
       <c r="H19" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.42</v>
+        <v>0.225</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>276000</v>
+        <v>170000</v>
       </c>
       <c r="L19" s="16" t="n">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
@@ -12361,7 +12381,7 @@
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr"/>
@@ -12377,7 +12397,7 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -12392,21 +12412,21 @@
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr"/>
       <c r="H20" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="J20" s="17" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="K20" s="16" t="n">
-        <v>138000</v>
+        <v>276000</v>
       </c>
       <c r="L20" s="16" t="n">
         <v>836</v>
@@ -12434,59 +12454,51 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная ДУ 80, сталь</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr"/>
       <c r="H21" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>0.03</v>
+        <v>0.21</v>
       </c>
       <c r="K21" s="16" t="n">
-        <v>22000</v>
+        <v>138000</v>
       </c>
       <c r="L21" s="16" t="n">
-        <v>786</v>
+        <v>836</v>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O21" s="19" t="inlineStr">
-        <is>
-          <t>сталь, в этот раз не грузим</t>
-        </is>
-      </c>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n">
@@ -12499,39 +12511,39 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr"/>
       <c r="H22" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>0.045</v>
+        <v>0.14</v>
       </c>
       <c r="K22" s="16" t="n">
-        <v>35000</v>
+        <v>75000</v>
       </c>
       <c r="L22" s="16" t="n">
-        <v>778</v>
+        <v>682</v>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
@@ -12540,7 +12552,7 @@
       </c>
       <c r="N22" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr"/>
@@ -12556,7 +12568,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -12571,24 +12583,24 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr"/>
       <c r="H23" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>75000</v>
+        <v>30000</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>682</v>
+        <v>545</v>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
@@ -12597,7 +12609,7 @@
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr"/>
@@ -12613,57 +12625,49 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Ду100</t>
-        </is>
-      </c>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr"/>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr"/>
       <c r="H24" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="L24" s="16" t="n">
-        <v>667</v>
+        <v>500</v>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
         <is>
-          <t>сталь, в этот раз не грузим</t>
+          <t>клапанная коробка, следующей отгрузкой</t>
         </is>
       </c>
     </row>
@@ -12678,51 +12682,51 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr"/>
       <c r="H25" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K25" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L25" s="16" t="n">
-        <v>545</v>
-      </c>
+        <v>0.036</v>
+      </c>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr"/>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O25" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
@@ -12735,43 +12739,51 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr"/>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>Задвижки (желтая) ок. крышек</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr"/>
       <c r="H26" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>520</v>
+        <v>360</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="K26" s="16" t="n"/>
       <c r="L26" s="16" t="n"/>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr"/>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O26" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
@@ -12784,12 +12796,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -12799,18 +12811,18 @@
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr"/>
       <c r="H27" s="14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.495</v>
+        <v>0.045</v>
       </c>
       <c r="K27" s="16" t="n"/>
       <c r="L27" s="16" t="n"/>
@@ -12821,10 +12833,14 @@
       </c>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr"/>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O27" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
@@ -12837,7 +12853,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -12847,29 +12863,29 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду100</t>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr"/>
       <c r="H28" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>0.045</v>
+        <v>0.024</v>
       </c>
       <c r="K28" s="16" t="n"/>
       <c r="L28" s="16" t="n"/>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
@@ -12894,40 +12910,36 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>клапан быстрозапорный</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr"/>
       <c r="H29" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K29" s="16" t="n">
-        <v>175000</v>
-      </c>
-      <c r="L29" s="16" t="n">
-        <v>1750</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n"/>
       <c r="M29" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -12935,10 +12947,14 @@
       </c>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr"/>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O29" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
@@ -12951,40 +12967,36 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>клапан быстрозапорный</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr"/>
       <c r="H30" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K30" s="16" t="n">
-        <v>90000</v>
-      </c>
-      <c r="L30" s="16" t="n">
-        <v>1607</v>
-      </c>
+        <v>0.012</v>
+      </c>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
       <c r="M30" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -12992,10 +13004,14 @@
       </c>
       <c r="N30" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr"/>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O30" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
@@ -13008,12 +13024,12 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -13023,25 +13039,21 @@
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr"/>
       <c r="H31" s="14" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>924</v>
+        <v>50</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="K31" s="16" t="n">
-        <v>1485000</v>
-      </c>
-      <c r="L31" s="16" t="n">
-        <v>1607</v>
-      </c>
+        <v>0.024</v>
+      </c>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="16" t="n"/>
       <c r="M31" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -13052,7 +13064,11 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O31" s="14" t="inlineStr"/>
+      <c r="O31" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
@@ -13065,40 +13081,36 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру25</t>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr"/>
       <c r="H32" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J32" s="17" t="n">
         <v>0.06</v>
       </c>
-      <c r="K32" s="16" t="n">
-        <v>112500</v>
-      </c>
-      <c r="L32" s="16" t="n">
-        <v>1607</v>
-      </c>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="16" t="n"/>
       <c r="M32" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -13109,7 +13121,11 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O32" s="14" t="inlineStr"/>
+      <c r="O32" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
@@ -13122,40 +13138,36 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr"/>
       <c r="H33" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="K33" s="16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="L33" s="16" t="n">
-        <v>1607</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="K33" s="16" t="n"/>
+      <c r="L33" s="16" t="n"/>
       <c r="M33" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -13163,10 +13175,14 @@
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr"/>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O33" s="19" t="inlineStr">
+        <is>
+          <t>клапанная коробка, следующей отгрузкой</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">
@@ -13179,39 +13195,39 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>Захлопка Ду50Ру6 - БРАК</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr"/>
       <c r="H34" s="14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>0.036</v>
+        <v>0.1</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>52500</v>
+        <v>175000</v>
       </c>
       <c r="L34" s="16" t="n">
-        <v>1458</v>
+        <v>1750</v>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
@@ -13220,7 +13236,7 @@
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O34" s="14" t="inlineStr"/>
@@ -13236,39 +13252,39 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr"/>
       <c r="H35" s="14" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>1372</v>
+        <v>56</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>1.176</v>
+        <v>0.06</v>
       </c>
       <c r="K35" s="16" t="n">
-        <v>1960000</v>
+        <v>90000</v>
       </c>
       <c r="L35" s="16" t="n">
-        <v>1429</v>
+        <v>1607</v>
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
@@ -13277,7 +13293,7 @@
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="O35" s="14" t="inlineStr"/>
@@ -13293,12 +13309,12 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -13308,24 +13324,24 @@
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr"/>
       <c r="H36" s="14" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>100</v>
+        <v>924</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>0.048</v>
+        <v>0.792</v>
       </c>
       <c r="K36" s="16" t="n">
-        <v>140000</v>
+        <v>1485000</v>
       </c>
       <c r="L36" s="16" t="n">
-        <v>1400</v>
+        <v>1607</v>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
@@ -13337,11 +13353,7 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O36" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
@@ -13354,7 +13366,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -13364,29 +13376,29 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65</t>
+          <t>Клапан фланцевый проходной Ду50 Ру25</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr"/>
       <c r="H37" s="14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="K37" s="16" t="n">
-        <v>675000</v>
+        <v>112500</v>
       </c>
       <c r="L37" s="16" t="n">
-        <v>1350</v>
+        <v>1607</v>
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
@@ -13411,39 +13423,39 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr"/>
       <c r="H38" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="16" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>27000</v>
+        <v>45000</v>
       </c>
       <c r="L38" s="16" t="n">
-        <v>1350</v>
+        <v>1607</v>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
@@ -13452,7 +13464,7 @@
       </c>
       <c r="N38" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="O38" s="14" t="inlineStr"/>
@@ -13468,39 +13480,39 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Захлопка Ду50Ру6 - БРАК</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr"/>
       <c r="H39" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" s="16" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="J39" s="17" t="n">
-        <v>0.06</v>
+        <v>0.036</v>
       </c>
       <c r="K39" s="16" t="n">
-        <v>120000</v>
+        <v>52500</v>
       </c>
       <c r="L39" s="16" t="n">
-        <v>1333</v>
+        <v>1458</v>
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
@@ -13509,14 +13521,10 @@
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O39" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -13529,7 +13537,7 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -13539,29 +13547,29 @@
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду70 Ру10</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr"/>
       <c r="H40" s="14" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="I40" s="16" t="n">
-        <v>115</v>
+        <v>1372</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>0.11</v>
+        <v>1.176</v>
       </c>
       <c r="K40" s="16" t="n">
-        <v>150000</v>
+        <v>1960000</v>
       </c>
       <c r="L40" s="16" t="n">
-        <v>1304</v>
+        <v>1429</v>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
@@ -13570,7 +13578,7 @@
       </c>
       <c r="N40" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O40" s="14" t="inlineStr"/>
@@ -13586,7 +13594,7 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -13596,29 +13604,29 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду70 Ру10</t>
+          <t>Клапан фланцевый проходной Ду65</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr"/>
       <c r="H41" s="14" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I41" s="16" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>0.044</v>
+        <v>0.5</v>
       </c>
       <c r="K41" s="16" t="n">
-        <v>60000</v>
+        <v>675000</v>
       </c>
       <c r="L41" s="16" t="n">
-        <v>1304</v>
+        <v>1350</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
@@ -13643,7 +13651,7 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
@@ -13653,29 +13661,29 @@
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+          <t>Клапан фланцевый проходной Ду65 Ру10</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr"/>
       <c r="H42" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>0.096</v>
+        <v>0.02</v>
       </c>
       <c r="K42" s="16" t="n">
-        <v>144000</v>
+        <v>27000</v>
       </c>
       <c r="L42" s="16" t="n">
-        <v>1286</v>
+        <v>1350</v>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
@@ -13684,7 +13692,7 @@
       </c>
       <c r="N42" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O42" s="14" t="inlineStr"/>
@@ -13700,7 +13708,7 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -13710,29 +13718,29 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80</t>
+          <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr"/>
       <c r="H43" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="K43" s="16" t="n">
-        <v>216000</v>
+        <v>150000</v>
       </c>
       <c r="L43" s="16" t="n">
-        <v>1286</v>
+        <v>1304</v>
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
@@ -13757,7 +13765,7 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
@@ -13767,29 +13775,29 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
+          <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr"/>
       <c r="H44" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="K44" s="16" t="n">
-        <v>32000</v>
+        <v>60000</v>
       </c>
       <c r="L44" s="16" t="n">
-        <v>1143</v>
+        <v>1304</v>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
@@ -13798,7 +13806,7 @@
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O44" s="14" t="inlineStr"/>
@@ -13814,7 +13822,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -13829,28 +13837,24 @@
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>0.024</v>
+        <v>0.096</v>
       </c>
       <c r="K45" s="16" t="n">
-        <v>30000</v>
+        <v>144000</v>
       </c>
       <c r="L45" s="16" t="n">
-        <v>1071</v>
+        <v>1286</v>
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
@@ -13862,11 +13866,7 @@
           <t>Склад 1А/1Б</t>
         </is>
       </c>
-      <c r="O45" s="19" t="inlineStr">
-        <is>
-          <t>сталь, в этот раз не грузим</t>
-        </is>
-      </c>
+      <c r="O45" s="14" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n">
@@ -13879,12 +13879,12 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -13894,24 +13894,24 @@
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Клапан фланцевый проходной Ду80</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr"/>
       <c r="H46" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="K46" s="16" t="n">
-        <v>88000</v>
+        <v>216000</v>
       </c>
       <c r="L46" s="16" t="n">
-        <v>978</v>
+        <v>1286</v>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
@@ -13923,11 +13923,7 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O46" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n">
@@ -13940,55 +13936,47 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr"/>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Электропривод к задвижке</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr"/>
       <c r="H47" s="14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>675</v>
+        <v>40</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
       <c r="K47" s="16" t="n">
-        <v>660000</v>
+        <v>50000</v>
       </c>
       <c r="L47" s="16" t="n">
-        <v>978</v>
+        <v>1250</v>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O47" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+          <t>Гараж 2</t>
+        </is>
+      </c>
+      <c r="O47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n">
@@ -14001,12 +13989,12 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
@@ -14016,24 +14004,24 @@
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+          <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr"/>
       <c r="H48" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K48" s="16" t="n">
-        <v>64000</v>
+        <v>32000</v>
       </c>
       <c r="L48" s="16" t="n">
-        <v>914</v>
+        <v>1143</v>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
@@ -14042,7 +14030,7 @@
       </c>
       <c r="N48" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O48" s="14" t="inlineStr"/>
@@ -14058,22 +14046,22 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду60</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr"/>
@@ -14081,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" s="17" t="n">
         <v>0.02</v>
@@ -14090,7 +14078,7 @@
         <v>18000</v>
       </c>
       <c r="L49" s="16" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
@@ -14115,7 +14103,7 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
@@ -14123,10 +14111,14 @@
           <t>клапан фланцевый</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr"/>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -14138,25 +14130,25 @@
         <v>2</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="K50" s="16" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="L50" s="16" t="n">
-        <v>900</v>
+        <v>1071</v>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N50" s="14" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O50" s="19" t="inlineStr">
@@ -14176,7 +14168,7 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -14186,29 +14178,29 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F51" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr"/>
       <c r="H51" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>0.012</v>
+        <v>0.06</v>
       </c>
       <c r="K51" s="16" t="n">
-        <v>17500</v>
+        <v>64000</v>
       </c>
       <c r="L51" s="16" t="n">
-        <v>875</v>
+        <v>914</v>
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
@@ -14233,22 +14225,22 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr"/>
@@ -14259,13 +14251,13 @@
         <v>20</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K52" s="16" t="n">
-        <v>17500</v>
+        <v>18000</v>
       </c>
       <c r="L52" s="16" t="n">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
@@ -14274,7 +14266,7 @@
       </c>
       <c r="N52" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O52" s="14" t="inlineStr"/>
@@ -14290,7 +14282,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -14298,14 +14290,10 @@
           <t>клапан фланцевый</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
+      <c r="E53" s="14" t="inlineStr"/>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
+          <t>Клапан проходной фланцевый сталь</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -14314,28 +14302,28 @@
         </is>
       </c>
       <c r="H53" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J53" s="17" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K53" s="16" t="n">
-        <v>22000</v>
+        <v>36000</v>
       </c>
       <c r="L53" s="16" t="n">
-        <v>786</v>
+        <v>900</v>
       </c>
       <c r="M53" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Фойе</t>
         </is>
       </c>
       <c r="O53" s="19" t="inlineStr">
@@ -14355,43 +14343,39 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr"/>
       <c r="H54" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="K54" s="16" t="n">
-        <v>22000</v>
+        <v>17500</v>
       </c>
       <c r="L54" s="16" t="n">
-        <v>786</v>
+        <v>875</v>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
@@ -14400,14 +14384,10 @@
       </c>
       <c r="N54" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O54" s="19" t="inlineStr">
-        <is>
-          <t>сталь, в этот раз не грузим</t>
-        </is>
-      </c>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O54" s="14" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n">
@@ -14420,12 +14400,12 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -14435,24 +14415,24 @@
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr"/>
       <c r="H55" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="K55" s="16" t="n">
-        <v>45000</v>
+        <v>17500</v>
       </c>
       <c r="L55" s="16" t="n">
-        <v>536</v>
+        <v>875</v>
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
@@ -14461,7 +14441,7 @@
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O55" s="14" t="inlineStr"/>
@@ -14477,39 +14457,43 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr"/>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr"/>
       <c r="H56" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K56" s="16" t="n">
-        <v>20000</v>
+        <v>48000</v>
       </c>
       <c r="L56" s="16" t="n">
-        <v>500</v>
+        <v>857</v>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N56" s="14" t="inlineStr">
@@ -14517,11 +14501,7 @@
           <t>Склад 1А/1Б</t>
         </is>
       </c>
-      <c r="O56" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O56" s="14" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n">
@@ -14534,7 +14514,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -14544,29 +14524,33 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="H57" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K57" s="16" t="n">
-        <v>19500</v>
+        <v>22000</v>
       </c>
       <c r="L57" s="16" t="n">
-        <v>488</v>
+        <v>786</v>
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
@@ -14578,7 +14562,11 @@
           <t>Склад 1А/1Б</t>
         </is>
       </c>
-      <c r="O57" s="14" t="inlineStr"/>
+      <c r="O57" s="19" t="inlineStr">
+        <is>
+          <t>сталь, в этот раз не грузим</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n">
@@ -14591,7 +14579,7 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -14601,29 +14589,33 @@
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="H58" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K58" s="16" t="n">
-        <v>9750</v>
+        <v>22000</v>
       </c>
       <c r="L58" s="16" t="n">
-        <v>488</v>
+        <v>786</v>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
@@ -14635,7 +14627,11 @@
           <t>Склад 1А/1Б</t>
         </is>
       </c>
-      <c r="O58" s="14" t="inlineStr"/>
+      <c r="O58" s="19" t="inlineStr">
+        <is>
+          <t>сталь, в этот раз не грузим</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n">
@@ -14648,43 +14644,59 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>клапан без описания — уточнить</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr"/>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>Клапан</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr"/>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="H59" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="16" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="K59" s="16" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L59" s="16" t="n">
+        <v>786</v>
+      </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N59" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="O59" s="14" t="inlineStr"/>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O59" s="19" t="inlineStr">
+        <is>
+          <t>сталь, в этот раз не грузим</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n">
@@ -14697,40 +14709,48 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>клапан электромагнитный</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="inlineStr"/>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr"/>
       <c r="H60" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K60" s="16" t="n"/>
-      <c r="L60" s="16" t="n"/>
+        <v>0.045</v>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L60" s="16" t="n">
+        <v>778</v>
+      </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N60" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O60" s="14" t="inlineStr"/>
@@ -14746,47 +14766,59 @@
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>клапан паровой</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr"/>
+          <t>Клинкет Ду 100, сталь</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="H61" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K61" s="16" t="n"/>
-      <c r="L61" s="16" t="n"/>
+        <v>0.09</v>
+      </c>
+      <c r="K61" s="16" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L61" s="16" t="n">
+        <v>667</v>
+      </c>
       <c r="M61" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="O61" s="14" t="inlineStr"/>
+          <t>Фойе</t>
+        </is>
+      </c>
+      <c r="O61" s="19" t="inlineStr">
+        <is>
+          <t>сталь, в этот раз не грузим</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n">
@@ -14799,12 +14831,12 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -14814,21 +14846,25 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr"/>
       <c r="H62" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K62" s="16" t="n"/>
-      <c r="L62" s="16" t="n"/>
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K62" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="L62" s="16" t="n">
+        <v>536</v>
+      </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -14836,7 +14872,7 @@
       </c>
       <c r="N62" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O62" s="14" t="inlineStr"/>
@@ -14852,36 +14888,40 @@
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr"/>
       <c r="H63" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="16" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K63" s="16" t="n"/>
-      <c r="L63" s="16" t="n"/>
+        <v>0.04</v>
+      </c>
+      <c r="K63" s="16" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L63" s="16" t="n">
+        <v>488</v>
+      </c>
       <c r="M63" s="15" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -14889,7 +14929,7 @@
       </c>
       <c r="N63" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O63" s="14" t="inlineStr"/>
@@ -14905,18 +14945,22 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>клапан без описания — уточнить</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="inlineStr"/>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Ду65</t>
+        </is>
+      </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr"/>
@@ -14924,21 +14968,25 @@
         <v>1</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K64" s="16" t="n"/>
-      <c r="L64" s="16" t="n"/>
+        <v>0.02</v>
+      </c>
+      <c r="K64" s="16" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L64" s="16" t="n">
+        <v>488</v>
+      </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N64" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O64" s="14" t="inlineStr"/>
@@ -14954,29 +15002,29 @@
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
         <is>
-          <t>клапан электромагнитный</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr"/>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr"/>
       <c r="H65" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I65" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J65" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="K65" s="16" t="n"/>
       <c r="L65" s="16" t="n"/>
@@ -14987,7 +15035,7 @@
       </c>
       <c r="N65" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="O65" s="14" t="inlineStr"/>
@@ -15003,39 +15051,35 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr"/>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr"/>
       <c r="H66" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66" s="16" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="K66" s="16" t="n"/>
       <c r="L66" s="16" t="n"/>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N66" s="14" t="inlineStr">
@@ -15043,11 +15087,7 @@
           <t>Склад 2</t>
         </is>
       </c>
-      <c r="O66" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O66" s="14" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n">
@@ -15060,33 +15100,33 @@
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан паровой</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr"/>
       <c r="H67" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I67" s="16" t="n">
-        <v>360</v>
+        <v>5</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="K67" s="16" t="n"/>
       <c r="L67" s="16" t="n"/>
@@ -15100,11 +15140,7 @@
           <t>Склад 2</t>
         </is>
       </c>
-      <c r="O67" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O67" s="14" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n">
@@ -15117,12 +15153,12 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -15132,18 +15168,18 @@
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr"/>
       <c r="H68" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" s="16" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>0.024</v>
+        <v>0.012</v>
       </c>
       <c r="K68" s="16" t="n"/>
       <c r="L68" s="16" t="n"/>
@@ -15157,11 +15193,7 @@
           <t>Склад 2</t>
         </is>
       </c>
-      <c r="O68" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O68" s="14" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n">
@@ -15174,33 +15206,33 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr"/>
       <c r="H69" s="14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I69" s="16" t="n">
-        <v>585</v>
+        <v>14</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>0.39</v>
+        <v>0.012</v>
       </c>
       <c r="K69" s="16" t="n"/>
       <c r="L69" s="16" t="n"/>
@@ -15214,11 +15246,7 @@
           <t>Склад 2</t>
         </is>
       </c>
-      <c r="O69" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O69" s="14" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n">
@@ -15231,22 +15259,18 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr"/>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr"/>
@@ -15254,28 +15278,24 @@
         <v>1</v>
       </c>
       <c r="I70" s="16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="K70" s="16" t="n"/>
       <c r="L70" s="16" t="n"/>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N70" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O70" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O70" s="14" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
@@ -15288,39 +15308,35 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E71" s="14" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr"/>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
+          <t>Клапан электромагнитный б/у</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr"/>
       <c r="H71" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I71" s="16" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J71" s="17" t="n">
-        <v>0.024</v>
+        <v>0.04</v>
       </c>
       <c r="K71" s="16" t="n"/>
       <c r="L71" s="16" t="n"/>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N71" s="14" t="inlineStr">
@@ -15328,11 +15344,7 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O71" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O71" s="14" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n">
@@ -15345,39 +15357,35 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr"/>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+          <t>Задвижки (желтая) ок. крышек</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr"/>
       <c r="H72" s="14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I72" s="16" t="n">
-        <v>90</v>
+        <v>520</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="K72" s="16" t="n"/>
       <c r="L72" s="16" t="n"/>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="N72" s="14" t="inlineStr">
@@ -15385,11 +15393,7 @@
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="O72" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+      <c r="O72" s="14" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
@@ -15402,51 +15406,47 @@
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr"/>
       <c r="H73" s="14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I73" s="16" t="n">
-        <v>135</v>
+        <v>495</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>0.09</v>
+        <v>0.495</v>
       </c>
       <c r="K73" s="16" t="n"/>
       <c r="L73" s="16" t="n"/>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O73" s="19" t="inlineStr">
-        <is>
-          <t>клапанная коробка, следующей отгрузкой</t>
-        </is>
-      </c>
+          <t>Склад электрики</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Задвижки и клинкеты Ду200, 250, 300, 350</t>
+          <t>Клинкеты Ду200, 250, 300, 350 — один слой</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
+          <t>Необрезная доска 25 мм сплошным настилом поверх слоя</t>
         </is>
       </c>
       <c r="D101" s="16" t="n">
@@ -16747,12 +16747,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
+          <t>Клапанные коробки и тяжелая арматура от Ду100</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -16761,27 +16761,27 @@
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>3290</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Ящики с мелкой арматурой до Ду80</t>
+          <t>Ящики с мелкой арматурой, включая клинкеты до Ду150</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Сплошной настил доской по верху ящиков, под верхний ярус</t>
+          <t>Два яруса ящиков высотой не больше 0,91 м каждый</t>
         </is>
       </c>
       <c r="D103" s="16" t="n">
-        <v>7091</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="104">

--- a/outputs/marine_equipment/План_2_контейнера.xlsx
+++ b/outputs/marine_equipment/План_2_контейнера.xlsx
@@ -15066,7 +15066,11 @@
       <c r="J99" s="33" t="n">
         <v>0.13</v>
       </c>
-      <c r="K99" s="18" t="inlineStr"/>
+      <c r="K99" s="34" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="L99" s="19" t="inlineStr">
         <is>
           <t>Б. Добор со склада</t>
